--- a/data/raw/inventory/Week 30/Tonor/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 30/Tonor/Seller FBA Inventory (SP-API).xlsx
@@ -1019,7 +1019,7 @@
         <v>123</v>
       </c>
       <c r="F10" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>123</v>

--- a/data/raw/inventory/Week 30/Tonor/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 30/Tonor/Seller FBA Inventory (SP-API).xlsx
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F8" t="n">
         <v>15</v>
@@ -907,10 +907,10 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F10" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1031,10 +1031,10 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1391,7 +1391,7 @@
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1412,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>13</v>
       </c>
       <c r="F19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1589,7 +1589,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
         <v>13</v>
